--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_163_R17.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_163_R17.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.966</v>
+        <v>4.418</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7111</v>
+        <v>3.4319</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2549</v>
+        <v>0.9861</v>
       </c>
       <c r="G2" t="n">
         <v>0.9550999999999999</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1204</v>
+        <v>-0.6684</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0395</v>
+        <v>-0.2396</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1599</v>
+        <v>-0.4288</v>
       </c>
       <c r="V2" t="n">
         <v>2.5077</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0605</v>
+        <v>3.5301</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6908</v>
+        <v>4.194</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6303</v>
+        <v>-0.6639</v>
       </c>
       <c r="G3" t="n">
         <v>1.0804</v>
@@ -688,13 +688,13 @@
         <v>3.0154</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5714</v>
+        <v>-1.1018</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3285</v>
+        <v>-0.8252</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2429</v>
+        <v>-0.2765</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3899</v>
+        <v>3.4218</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7977</v>
+        <v>2.4936</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.9282</v>
       </c>
       <c r="G4" t="n">
         <v>1.8276</v>
@@ -766,13 +766,13 @@
         <v>2.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9892</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4031</v>
+        <v>-0.7073</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.586</v>
+        <v>-0.25</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1437</v>
+        <v>3.3449</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2135</v>
+        <v>3.3318</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3572</v>
+        <v>0.0131</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1214</v>
+        <v>1.0797</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2654</v>
+        <v>1.7189</v>
       </c>
       <c r="I5" t="n">
-        <v>0.144</v>
+        <v>-0.6391</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4938</v>
+        <v>2.5277</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3466</v>
+        <v>3.3176</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1472</v>
+        <v>-0.7899</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6152</v>
+        <v>-1.448</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.612</v>
+        <v>-1.5987</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0033</v>
+        <v>0.1507</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.232</v>
+        <v>0.232</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6389</v>
+        <v>-0.3637</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6844</v>
+        <v>0.0514</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9545</v>
+        <v>-0.4151</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1418</v>
+        <v>2.3969</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>P. KALAITZAKIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1368</v>
+        <v>1.1767</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3253</v>
+        <v>0.5406</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1885</v>
+        <v>0.6361</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0797</v>
+        <v>0.766</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7189</v>
+        <v>-0.0371</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6391</v>
+        <v>0.8031</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5277</v>
+        <v>1.37</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3176</v>
+        <v>0.3529</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7899</v>
+        <v>1.0171</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.448</v>
+        <v>-0.604</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5987</v>
+        <v>-0.39</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1507</v>
+        <v>-0.214</v>
       </c>
       <c r="P6" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5718</v>
+        <v>-0.5171</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.955</v>
+        <v>-0.5975</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6168</v>
+        <v>0.0804</v>
       </c>
       <c r="V6" t="n">
-        <v>2.3969</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. KALAITZAKIS</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1692</v>
+        <v>0.6182</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4659</v>
+        <v>-0.6972</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7033</v>
+        <v>1.3154</v>
       </c>
       <c r="G7" t="n">
-        <v>0.766</v>
+        <v>-0.1214</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0371</v>
+        <v>-0.2654</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8031</v>
+        <v>0.144</v>
       </c>
       <c r="J7" t="n">
-        <v>1.37</v>
+        <v>0.4938</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3529</v>
+        <v>0.3466</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0171</v>
+        <v>0.1472</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.604</v>
+        <v>-0.6152</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.39</v>
+        <v>-0.612</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.214</v>
+        <v>-0.0033</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5245</v>
+        <v>1.1134</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6721</v>
+        <v>0.2008</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1476</v>
+        <v>0.9127</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4888</v>
+        <v>0.1178</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9901</v>
+        <v>0.5182</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5012</v>
+        <v>-0.4004</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1303</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.1759</v>
       </c>
       <c r="T8" t="n">
-        <v>0.637</v>
+        <v>0.1652</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V8" t="n">
         <v>1.0722</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.178</v>
+        <v>-0.5547</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5845</v>
+        <v>0.0339</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4065</v>
+        <v>-0.5887</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1667</v>
+        <v>-2.8291</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5042</v>
+        <v>-4.4587</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6625</v>
+        <v>1.6296</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6804</v>
+        <v>-1.6886</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9677</v>
+        <v>-2.9031</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7127</v>
+        <v>1.2146</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4862</v>
+        <v>-1.1405</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5365</v>
+        <v>-1.5556</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0502</v>
+        <v>0.415</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8</v>
+        <v>-0.5838</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4402</v>
+        <v>0.1142</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3598</v>
+        <v>-0.698</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3247</v>
+        <v>1.4665</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5361</v>
+        <v>1.6083</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7886</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.512</v>
+        <v>-0.9353</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-1.5098</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9247</v>
+        <v>0.5745</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.8291</v>
+        <v>-2.1667</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.4587</v>
+        <v>-1.5042</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6296</v>
+        <v>-0.6625</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6886</v>
+        <v>-1.6804</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.9031</v>
+        <v>-0.9677</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2146</v>
+        <v>-0.7127</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1405</v>
+        <v>-0.4862</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5556</v>
+        <v>-0.5365</v>
       </c>
       <c r="O10" t="n">
-        <v>0.415</v>
+        <v>0.0502</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5411</v>
+        <v>-0.5573</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.507</v>
+        <v>-0.3655</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0341</v>
+        <v>-0.1918</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4665</v>
+        <v>1.3247</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6083</v>
+        <v>0.5361</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1418</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8347</v>
+        <v>-1.0791</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6459</v>
+        <v>-1.0247</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1888</v>
+        <v>-0.0544</v>
       </c>
       <c r="G11" t="n">
         <v>-0.45</v>
@@ -1312,13 +1312,13 @@
         <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9208</v>
+        <v>-0.1652</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5975</v>
+        <v>0.0237</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3233</v>
+        <v>-0.1889</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6235</v>
+        <v>-3.358</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9733</v>
+        <v>-2.8422</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6502</v>
+        <v>-0.5158</v>
       </c>
       <c r="G12" t="n">
         <v>-5.7293</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4279</v>
+        <v>-0.3066</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7512</v>
+        <v>-0.1177</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3233</v>
+        <v>-0.1889</v>
       </c>
       <c r="V12" t="n">
         <v>1.7501</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.2067</v>
+        <v>10.7004</v>
       </c>
       <c r="E13" t="n">
-        <v>6.976500000000001</v>
+        <v>8.4701</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2304</v>
+        <v>2.2302</v>
       </c>
       <c r="G13" t="n">
         <v>-6.718</v>
@@ -1441,10 +1441,10 @@
         <v>-2.894</v>
       </c>
       <c r="J13" t="n">
-        <v>4.007000000000001</v>
+        <v>4.006999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>6.0658</v>
+        <v>6.065799999999999</v>
       </c>
       <c r="L13" t="n">
         <v>-2.0588</v>
@@ -1456,7 +1456,7 @@
         <v>-9.889699999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8352999999999999</v>
+        <v>-0.8353</v>
       </c>
       <c r="P13" t="n">
         <v>10.4379</v>
@@ -1468,10 +1468,10 @@
         <v>15.0771</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.4255</v>
+        <v>-3.9318</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.7913</v>
+        <v>-2.2975</v>
       </c>
       <c r="U13" t="n">
         <v>-1.6341</v>
@@ -1483,7 +1483,7 @@
         <v>11.3999</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4875000000000002</v>
+        <v>-0.4875000000000003</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8177</v>
+        <v>2.431</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6113</v>
+        <v>0.2144</v>
       </c>
       <c r="F14" t="n">
-        <v>2.429</v>
+        <v>2.2166</v>
       </c>
       <c r="G14" t="n">
         <v>3.5188</v>
@@ -1546,13 +1546,13 @@
         <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0127</v>
+        <v>0.626</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0455</v>
+        <v>-0.2199</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0583</v>
+        <v>0.8459</v>
       </c>
       <c r="V14" t="n">
         <v>0.1418</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3346</v>
+        <v>1.9008</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2403</v>
+        <v>2.1223</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9056999999999999</v>
+        <v>-0.2215</v>
       </c>
       <c r="G15" t="n">
         <v>2.3582</v>
@@ -1624,13 +1624,13 @@
         <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1208</v>
+        <v>0.6871</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3778</v>
+        <v>0.2598</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.257</v>
+        <v>0.4272</v>
       </c>
       <c r="V15" t="n">
         <v>-1.6083</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0587</v>
+        <v>1.4341</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1122</v>
+        <v>1.9942</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0534</v>
+        <v>-0.5601</v>
       </c>
       <c r="G16" t="n">
         <v>3.8132</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3383</v>
+        <v>0.7136</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3031</v>
+        <v>0.1852</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0351</v>
+        <v>0.5285</v>
       </c>
       <c r="V16" t="n">
         <v>-2.3969</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.358</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9263</v>
+        <v>0.5725</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2373</v>
+        <v>-0.2145</v>
       </c>
       <c r="G17" t="n">
         <v>1.498</v>
@@ -1780,13 +1780,13 @@
         <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5157</v>
+        <v>0.1847</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4129</v>
+        <v>0.0591</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1028</v>
+        <v>0.1256</v>
       </c>
       <c r="V17" t="n">
         <v>-1.3247</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1768</v>
+        <v>-0.9701</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4579</v>
+        <v>1.1041</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6348</v>
+        <v>-2.0742</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0188</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4657</v>
+        <v>0.6723</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6765</v>
+        <v>0.3227</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2109</v>
+        <v>0.3497</v>
       </c>
       <c r="V18" t="n">
         <v>0.5361</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5199</v>
+        <v>-1.3226</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0004</v>
+        <v>-0.8824</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5195</v>
+        <v>-0.4402</v>
       </c>
       <c r="G19" t="n">
         <v>0.524</v>
@@ -1936,13 +1936,13 @@
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1365</v>
+        <v>1.3337</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2284</v>
+        <v>0.3464</v>
       </c>
       <c r="U19" t="n">
-        <v>0.908</v>
+        <v>0.9873</v>
       </c>
       <c r="V19" t="n">
         <v>-1.3247</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3067</v>
+        <v>-2.6399</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7705</v>
+        <v>-0.5109</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4638</v>
+        <v>-2.129</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2485</v>
+        <v>-1.7535</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5029</v>
+        <v>-0.3348</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2544</v>
+        <v>-1.4187</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7169</v>
+        <v>-0.4166</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1414</v>
+        <v>0.3697</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5754</v>
+        <v>-0.7863</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9654</v>
+        <v>-1.3369</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6443</v>
+        <v>-0.7045</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3211</v>
+        <v>-0.6323</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.0154</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.7112</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6067</v>
+        <v>0.1858</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8011</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>1.8055</v>
+        <v>0.2801</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.6495</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.5773</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>-1.0722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1618</v>
+        <v>-3.8159</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8647</v>
+        <v>-3.8321</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2971</v>
+        <v>0.0162</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7535</v>
+        <v>-0.2485</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3348</v>
+        <v>-0.5029</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4187</v>
+        <v>0.2544</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4166</v>
+        <v>0.7169</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3697</v>
+        <v>0.1414</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7863</v>
+        <v>0.5754</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3369</v>
+        <v>-0.9654</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7045</v>
+        <v>-0.6443</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6323</v>
+        <v>-0.3211</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.7112</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3361</v>
+        <v>2.0974</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4481</v>
+        <v>0.7395</v>
       </c>
       <c r="U21" t="n">
-        <v>0.112</v>
+        <v>1.3579</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0722</v>
+        <v>-2.6495</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-1.5773</v>
       </c>
       <c r="X21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.9416</v>
+        <v>-5.0094</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7202</v>
+        <v>-3.0125</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2214</v>
+        <v>-1.997</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9732</v>
@@ -2170,13 +2170,13 @@
         <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4349</v>
+        <v>0.4973</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6721</v>
+        <v>0.0356</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2372</v>
+        <v>0.4617</v>
       </c>
       <c r="V22" t="n">
         <v>-1.214</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.206800000000001</v>
+        <v>-7.633999999999999</v>
       </c>
       <c r="E23" t="n">
         <v>-2.2304</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.9764</v>
+        <v>-5.403700000000001</v>
       </c>
       <c r="G23" t="n">
         <v>6.718200000000001</v>
@@ -2248,13 +2248,13 @@
         <v>4.6392</v>
       </c>
       <c r="S23" t="n">
-        <v>5.4254</v>
+        <v>6.9979</v>
       </c>
       <c r="T23" t="n">
-        <v>1.6341</v>
+        <v>1.6342</v>
       </c>
       <c r="U23" t="n">
-        <v>3.791</v>
+        <v>5.363899999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-10.9124</v>
